--- a/artfynd/A 28240-2026 artfynd.xlsx
+++ b/artfynd/A 28240-2026 artfynd.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 28240-2026 artfynd.xlsx
+++ b/artfynd/A 28240-2026 artfynd.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 28240-2026 artfynd.xlsx
+++ b/artfynd/A 28240-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,61 +799,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134906633</v>
+        <v>135789062</v>
       </c>
       <c r="B3" t="n">
-        <v>45052</v>
+        <v>92059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102020</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 28240, Rönnäs, Hjorted, Sm</t>
+          <t>Rönnäs, Rönnäs, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578627</v>
+        <v>579085</v>
       </c>
       <c r="R3" t="n">
-        <v>6389724</v>
+        <v>6389916</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,12 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,23 +878,138 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135789062</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134906633</v>
+      </c>
+      <c r="B4" t="n">
+        <v>45052</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102020</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Smalsprötad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Zygaena osterodensis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Reiss, 1921</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 28240, Rönnäs, Hjorted, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>578627</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6389724</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134906633</t>
         </is>
@@ -917,6 +1019,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28240-2026 artfynd.xlsx
+++ b/artfynd/A 28240-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>135789062</v>
       </c>
       <c r="B3" t="n">
-        <v>92059</v>
+        <v>92061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28240-2026 artfynd.xlsx
+++ b/artfynd/A 28240-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>135789062</v>
       </c>
       <c r="B3" t="n">
-        <v>92061</v>
+        <v>92075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28240-2026 artfynd.xlsx
+++ b/artfynd/A 28240-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>135789062</v>
       </c>
       <c r="B3" t="n">
-        <v>92075</v>
+        <v>92076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28240-2026 artfynd.xlsx
+++ b/artfynd/A 28240-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>135789062</v>
       </c>
       <c r="B3" t="n">
-        <v>92076</v>
+        <v>92077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28240-2026 artfynd.xlsx
+++ b/artfynd/A 28240-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>135789062</v>
       </c>
       <c r="B3" t="n">
-        <v>92077</v>
+        <v>92078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28240-2026 artfynd.xlsx
+++ b/artfynd/A 28240-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>135789062</v>
       </c>
       <c r="B3" t="n">
-        <v>92078</v>
+        <v>92084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28240-2026 artfynd.xlsx
+++ b/artfynd/A 28240-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>135789062</v>
       </c>
       <c r="B3" t="n">
-        <v>92084</v>
+        <v>92085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
